--- a/wwwroot/template/NccMasterActions.xlsx
+++ b/wwwroot/template/NccMasterActions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\khanhmf\Cost Managerment\wwwroot\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A75AA75-233D-4E68-9F99-D9DA8F4AD600}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F95A555C-1434-4794-A793-BA5F15F78060}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{02617A9F-CB73-49CB-8458-E03BE0290D84}"/>
+    <workbookView xWindow="5880" yWindow="1725" windowWidth="21600" windowHeight="11295" xr2:uid="{02617A9F-CB73-49CB-8458-E03BE0290D84}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/wwwroot/template/NccMasterActions.xlsx
+++ b/wwwroot/template/NccMasterActions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\khanhmf\Cost Managerment\wwwroot\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F95A555C-1434-4794-A793-BA5F15F78060}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1614CE6-C4CA-483A-8171-B4E3B5DFBCD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5880" yWindow="1725" windowWidth="21600" windowHeight="11295" xr2:uid="{02617A9F-CB73-49CB-8458-E03BE0290D84}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{02617A9F-CB73-49CB-8458-E03BE0290D84}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -506,9 +506,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:I1" xr:uid="{DC46B6F2-E64A-41F2-A229-755E40FA07BF}"/>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A660" xr:uid="{479DB44A-465D-4AB7-89AD-67A69AC8F534}">
-      <formula1>"Thêm NCC vào chủng loại đã có,Thêm NCC mới,Xóa"</formula1>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1163:A1405" xr:uid="{9FEB4B37-99B8-44D2-9441-AA01DB765391}">
+      <formula1>"Thêm, Xóa chủng loại, Xóa nhà cung cấp"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A1162" xr:uid="{4C14639B-F2C1-4FDF-AA5F-72CD9251A4D6}">
+      <formula1>"Thêm, Xóa"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
